--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/170.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/170.xlsx
@@ -426,13 +426,13 @@
         <v>-9.330098724067602</v>
       </c>
       <c r="E2">
-        <v>-8.774925787798622</v>
+        <v>-7.783090353690645</v>
       </c>
       <c r="F2">
-        <v>-3.249887920719522</v>
+        <v>-2.631219539676763</v>
       </c>
       <c r="G2">
-        <v>-13.44480524748418</v>
+        <v>-13.43769088512028</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-9.53493413338817</v>
       </c>
       <c r="E3">
-        <v>-9.9079816838358</v>
+        <v>-8.45221314459001</v>
       </c>
       <c r="F3">
-        <v>-2.986106655296886</v>
+        <v>-2.707333237825741</v>
       </c>
       <c r="G3">
-        <v>-13.4553956826643</v>
+        <v>-13.1350904701032</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-9.755831391596967</v>
       </c>
       <c r="E4">
-        <v>-9.70259274521791</v>
+        <v>-9.616569852968205</v>
       </c>
       <c r="F4">
-        <v>-2.770124801814042</v>
+        <v>-2.733695606494146</v>
       </c>
       <c r="G4">
-        <v>-12.53802033991348</v>
+        <v>-12.82603780183008</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-9.925224060234866</v>
       </c>
       <c r="E5">
-        <v>-9.959456847880988</v>
+        <v>-8.22598869706283</v>
       </c>
       <c r="F5">
-        <v>-2.802630365728437</v>
+        <v>-2.416171280831072</v>
       </c>
       <c r="G5">
-        <v>-12.50176324516739</v>
+        <v>-11.41211042309843</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-10.01354759332443</v>
       </c>
       <c r="E6">
-        <v>-11.68224685698906</v>
+        <v>-10.10442688628854</v>
       </c>
       <c r="F6">
-        <v>-2.57686041783522</v>
+        <v>-2.508913099239206</v>
       </c>
       <c r="G6">
-        <v>-12.30107797457677</v>
+        <v>-11.09577455463891</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-9.980170483927933</v>
       </c>
       <c r="E7">
-        <v>-11.34580388058919</v>
+        <v>-11.1392330102553</v>
       </c>
       <c r="F7">
-        <v>-2.726539631315233</v>
+        <v>-2.722755366030291</v>
       </c>
       <c r="G7">
-        <v>-12.19593173770397</v>
+        <v>-11.94029472170699</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-9.805929085122429</v>
       </c>
       <c r="E8">
-        <v>-12.3978182057851</v>
+        <v>-12.37923787693163</v>
       </c>
       <c r="F8">
-        <v>-2.554799394433148</v>
+        <v>-2.573540970236459</v>
       </c>
       <c r="G8">
-        <v>-11.43649921208624</v>
+        <v>-11.86344702810389</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-9.478239166008349</v>
       </c>
       <c r="E9">
-        <v>-12.91553146823801</v>
+        <v>-11.92603725519199</v>
       </c>
       <c r="F9">
-        <v>-2.585314240011836</v>
+        <v>-2.044212607295471</v>
       </c>
       <c r="G9">
-        <v>-11.23667137279029</v>
+        <v>-10.30399468855696</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-8.994987647634927</v>
       </c>
       <c r="E10">
-        <v>-13.18471754867596</v>
+        <v>-13.43263791517388</v>
       </c>
       <c r="F10">
-        <v>-2.58474331402932</v>
+        <v>-2.456747410090546</v>
       </c>
       <c r="G10">
-        <v>-11.15763540858573</v>
+        <v>-10.07679194819678</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-8.37460479501107</v>
       </c>
       <c r="E11">
-        <v>-14.57868600313907</v>
+        <v>-14.90450517951694</v>
       </c>
       <c r="F11">
-        <v>-2.680540893001294</v>
+        <v>-2.190235835669692</v>
       </c>
       <c r="G11">
-        <v>-10.12409964395296</v>
+        <v>-9.675855088481185</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-7.654271149335071</v>
       </c>
       <c r="E12">
-        <v>-14.63964832023033</v>
+        <v>-15.42015798629636</v>
       </c>
       <c r="F12">
-        <v>-2.44296679306735</v>
+        <v>-2.424876912248243</v>
       </c>
       <c r="G12">
-        <v>-9.953427779221379</v>
+        <v>-8.962445766950401</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-6.881218293249427</v>
       </c>
       <c r="E13">
-        <v>-16.11486212686505</v>
+        <v>-16.00103893268226</v>
       </c>
       <c r="F13">
-        <v>-2.069825883065873</v>
+        <v>-1.870515701754861</v>
       </c>
       <c r="G13">
-        <v>-9.475673020812534</v>
+        <v>-9.61905605866391</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-6.120979127127909</v>
       </c>
       <c r="E14">
-        <v>-17.92978393965918</v>
+        <v>-16.64544984092176</v>
       </c>
       <c r="F14">
-        <v>-2.15611805913338</v>
+        <v>-1.923227769444347</v>
       </c>
       <c r="G14">
-        <v>-9.851492771521679</v>
+        <v>-8.867707885253077</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-5.446524686922969</v>
       </c>
       <c r="E15">
-        <v>-18.13717899226247</v>
+        <v>-15.66470011118457</v>
       </c>
       <c r="F15">
-        <v>-2.103950786278804</v>
+        <v>-1.923264194680402</v>
       </c>
       <c r="G15">
-        <v>-9.364389032509933</v>
+        <v>-8.871567981351868</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-4.924090466925795</v>
       </c>
       <c r="E16">
-        <v>-18.65625985386569</v>
+        <v>-17.79621207032893</v>
       </c>
       <c r="F16">
-        <v>-1.52776135715292</v>
+        <v>-1.483465102698079</v>
       </c>
       <c r="G16">
-        <v>-8.831927509064634</v>
+        <v>-8.843726293366597</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-4.612147448569584</v>
       </c>
       <c r="E17">
-        <v>-19.30243233849418</v>
+        <v>-19.24119378448845</v>
       </c>
       <c r="F17">
-        <v>-1.495859185192308</v>
+        <v>-1.257513028624587</v>
       </c>
       <c r="G17">
-        <v>-8.856279882051513</v>
+        <v>-8.084840007762846</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-4.550751066726007</v>
       </c>
       <c r="E18">
-        <v>-19.46047608136188</v>
+        <v>-20.10057588234608</v>
       </c>
       <c r="F18">
-        <v>-1.219995035487826</v>
+        <v>-1.080094414182694</v>
       </c>
       <c r="G18">
-        <v>-7.567994327626288</v>
+        <v>-7.564922141365845</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-4.750825482818429</v>
       </c>
       <c r="E19">
-        <v>-21.33617001533894</v>
+        <v>-21.28424200389298</v>
       </c>
       <c r="F19">
-        <v>-0.6156409803617675</v>
+        <v>-0.8252626708882059</v>
       </c>
       <c r="G19">
-        <v>-8.106682987230958</v>
+        <v>-7.74573420708422</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-5.199126730168255</v>
       </c>
       <c r="E20">
-        <v>-21.68453193532699</v>
+        <v>-22.29996966686543</v>
       </c>
       <c r="F20">
-        <v>-0.4428404523692963</v>
+        <v>-0.2821220168057125</v>
       </c>
       <c r="G20">
-        <v>-7.855074905155268</v>
+        <v>-8.218264924632091</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-5.857352503322329</v>
       </c>
       <c r="E21">
-        <v>-21.52644290771922</v>
+        <v>-22.02025941283365</v>
       </c>
       <c r="F21">
-        <v>-0.3085920774763675</v>
+        <v>-0.1080846144932831</v>
       </c>
       <c r="G21">
-        <v>-8.218738332644207</v>
+        <v>-8.19678941571884</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-6.661794370410508</v>
       </c>
       <c r="E22">
-        <v>-23.11490479233777</v>
+        <v>-23.13243904369547</v>
       </c>
       <c r="F22">
-        <v>-0.001342835792664303</v>
+        <v>0.2387746958414761</v>
       </c>
       <c r="G22">
-        <v>-8.187460298389174</v>
+        <v>-7.802169076892175</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-7.536586023582333</v>
       </c>
       <c r="E23">
-        <v>-23.42025073772696</v>
+        <v>-22.71648059219492</v>
       </c>
       <c r="F23">
-        <v>0.3041872931198293</v>
+        <v>0.2565969303608739</v>
       </c>
       <c r="G23">
-        <v>-8.174870293703325</v>
+        <v>-7.91538973433525</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-8.405594822191429</v>
       </c>
       <c r="E24">
-        <v>-23.23975934920325</v>
+        <v>-22.07961412165218</v>
       </c>
       <c r="F24">
-        <v>-0.1099803104740641</v>
+        <v>0.367202951495165</v>
       </c>
       <c r="G24">
-        <v>-8.291292248682876</v>
+        <v>-8.340771662312822</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-9.198223760923407</v>
       </c>
       <c r="E25">
-        <v>-23.69224900052368</v>
+        <v>-23.00936870558901</v>
       </c>
       <c r="F25">
-        <v>0.3250945867625032</v>
+        <v>0.3266664148835768</v>
       </c>
       <c r="G25">
-        <v>-8.469757137613906</v>
+        <v>-8.107593387254257</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-9.855957137299598</v>
       </c>
       <c r="E26">
-        <v>-23.51795709291646</v>
+        <v>-23.0907770828249</v>
       </c>
       <c r="F26">
-        <v>0.3183305787976613</v>
+        <v>0.1704892560325157</v>
       </c>
       <c r="G26">
-        <v>-9.149100945545589</v>
+        <v>-8.187996606766536</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-10.33874233323178</v>
       </c>
       <c r="E27">
-        <v>-23.6236607332035</v>
+        <v>-23.10603351175674</v>
       </c>
       <c r="F27">
-        <v>0.1224237814989285</v>
+        <v>0.2476410734090639</v>
       </c>
       <c r="G27">
-        <v>-9.046513760374655</v>
+        <v>-9.464768083806176</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-10.62504916670105</v>
       </c>
       <c r="E28">
-        <v>-23.43194325761477</v>
+        <v>-23.66710691283309</v>
       </c>
       <c r="F28">
-        <v>0.2121209252846302</v>
+        <v>0.08885317535640083</v>
       </c>
       <c r="G28">
-        <v>-9.296986325330373</v>
+        <v>-8.768725884174408</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-10.70986522300926</v>
       </c>
       <c r="E29">
-        <v>-22.99488664571248</v>
+        <v>-23.39544375711295</v>
       </c>
       <c r="F29">
-        <v>0.207764942164214</v>
+        <v>0.401221746411762</v>
       </c>
       <c r="G29">
-        <v>-9.414487518155726</v>
+        <v>-8.903895458542852</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-10.6060037464</v>
       </c>
       <c r="E30">
-        <v>-22.88817315572173</v>
+        <v>-22.91146762601718</v>
       </c>
       <c r="F30">
-        <v>0.4451782959477416</v>
+        <v>0.3896401050521533</v>
       </c>
       <c r="G30">
-        <v>-9.219992967723543</v>
+        <v>-8.401513551867371</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-10.33919959375288</v>
       </c>
       <c r="E31">
-        <v>-23.4000220443347</v>
+        <v>-22.44087313561409</v>
       </c>
       <c r="F31">
-        <v>0.04453950013648965</v>
+        <v>0.535946816785238</v>
       </c>
       <c r="G31">
-        <v>-8.892103295331967</v>
+        <v>-9.4444876818326</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-9.941532972276187</v>
       </c>
       <c r="E32">
-        <v>-22.63267665220897</v>
+        <v>-21.37607492829453</v>
       </c>
       <c r="F32">
-        <v>0.2805005955955592</v>
+        <v>0.426290227347253</v>
       </c>
       <c r="G32">
-        <v>-8.823465754666257</v>
+        <v>-8.764518180793996</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-9.450994311372444</v>
       </c>
       <c r="E33">
-        <v>-21.90518635982474</v>
+        <v>-21.32300574139864</v>
       </c>
       <c r="F33">
-        <v>0.3080618296419519</v>
+        <v>0.3211416567975663</v>
       </c>
       <c r="G33">
-        <v>-8.888759644337304</v>
+        <v>-8.407270590560163</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-8.906183342681631</v>
       </c>
       <c r="E34">
-        <v>-22.79499980301391</v>
+        <v>-21.57002494156904</v>
       </c>
       <c r="F34">
-        <v>0.1076668097788637</v>
+        <v>0.4611404678694558</v>
       </c>
       <c r="G34">
-        <v>-8.616636111554751</v>
+        <v>-8.62418415538429</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-8.340774845176368</v>
       </c>
       <c r="E35">
-        <v>-21.20700435121815</v>
+        <v>-20.79579626895165</v>
       </c>
       <c r="F35">
-        <v>0.2674532344112113</v>
+        <v>0.1956266281753284</v>
       </c>
       <c r="G35">
-        <v>-7.939348152402955</v>
+        <v>-8.914853364277839</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-7.784233846218502</v>
       </c>
       <c r="E36">
-        <v>-21.06879079603005</v>
+        <v>-20.71552453869168</v>
       </c>
       <c r="F36">
-        <v>0.2032743440409855</v>
+        <v>0.590415214334947</v>
       </c>
       <c r="G36">
-        <v>-8.052558878209412</v>
+        <v>-7.748713698069563</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-7.256555257511027</v>
       </c>
       <c r="E37">
-        <v>-21.26659001221108</v>
+        <v>-20.14055325088579</v>
       </c>
       <c r="F37">
-        <v>0.1006304043965663</v>
+        <v>0.4806604351302047</v>
       </c>
       <c r="G37">
-        <v>-7.532852886726925</v>
+        <v>-7.768901404768039</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-6.768280943311852</v>
       </c>
       <c r="E38">
-        <v>-20.18271787237121</v>
+        <v>-19.75445102851781</v>
       </c>
       <c r="F38">
-        <v>0.2915730755033542</v>
+        <v>0.1248175529901152</v>
       </c>
       <c r="G38">
-        <v>-7.400685977162602</v>
+        <v>-8.115310268906297</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-6.326646972315919</v>
       </c>
       <c r="E39">
-        <v>-19.90939729516426</v>
+        <v>-19.35364032257291</v>
       </c>
       <c r="F39">
-        <v>0.20904774395572</v>
+        <v>0.8920225036948971</v>
       </c>
       <c r="G39">
-        <v>-7.519806026756657</v>
+        <v>-7.407075330053395</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-5.931338048503622</v>
       </c>
       <c r="E40">
-        <v>-19.56707635950243</v>
+        <v>-18.93277753372206</v>
       </c>
       <c r="F40">
-        <v>0.162139958446319</v>
+        <v>0.3672829286438946</v>
       </c>
       <c r="G40">
-        <v>-7.609021918494476</v>
+        <v>-6.360194756351825</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-5.575784588303854</v>
       </c>
       <c r="E41">
-        <v>-19.23167493212433</v>
+        <v>-18.01585211664896</v>
       </c>
       <c r="F41">
-        <v>0.007027049970433176</v>
+        <v>0.2898721753501722</v>
       </c>
       <c r="G41">
-        <v>-7.471879258984628</v>
+        <v>-6.59559771801278</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-5.254672614249209</v>
       </c>
       <c r="E42">
-        <v>-20.21059515836243</v>
+        <v>-18.06002285211978</v>
       </c>
       <c r="F42">
-        <v>0.3002652454202435</v>
+        <v>0.02347937887297588</v>
       </c>
       <c r="G42">
-        <v>-7.588738205975361</v>
+        <v>-6.802725310222821</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-4.960063741058094</v>
       </c>
       <c r="E43">
-        <v>-18.7152477562896</v>
+        <v>-17.76892801443272</v>
       </c>
       <c r="F43">
-        <v>-0.02307128095249352</v>
+        <v>0.3292573577612358</v>
       </c>
       <c r="G43">
-        <v>-7.006284134341528</v>
+        <v>-7.703216870723359</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-4.682644122001617</v>
       </c>
       <c r="E44">
-        <v>-17.32664101505157</v>
+        <v>-16.64056361746749</v>
       </c>
       <c r="F44">
-        <v>0.2326196228011207</v>
+        <v>-0.1338689305025527</v>
       </c>
       <c r="G44">
-        <v>-7.198881742179708</v>
+        <v>-7.274236379744599</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-4.419589909008391</v>
       </c>
       <c r="E45">
-        <v>-18.02815145205379</v>
+        <v>-15.42262147615653</v>
       </c>
       <c r="F45">
-        <v>-0.07996987522944426</v>
+        <v>0.05102240030134102</v>
       </c>
       <c r="G45">
-        <v>-7.132266944838493</v>
+        <v>-6.943714823649303</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-4.171387628171514</v>
       </c>
       <c r="E46">
-        <v>-17.53002836815807</v>
+        <v>-15.51600766714271</v>
       </c>
       <c r="F46">
-        <v>-0.2870307132906171</v>
+        <v>0.3183955107401943</v>
       </c>
       <c r="G46">
-        <v>-7.452707889766709</v>
+        <v>-6.997928317400408</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-3.94005521325846</v>
       </c>
       <c r="E47">
-        <v>-17.51287450861701</v>
+        <v>-15.58666544708439</v>
       </c>
       <c r="F47">
-        <v>-0.1475917422598355</v>
+        <v>-0.4471829739894312</v>
       </c>
       <c r="G47">
-        <v>-7.699605065540014</v>
+        <v>-7.345525667387265</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-3.733917241976667</v>
       </c>
       <c r="E48">
-        <v>-15.66369931842887</v>
+        <v>-15.18124475459969</v>
       </c>
       <c r="F48">
-        <v>-0.02250114682293532</v>
+        <v>-0.1037975225801885</v>
       </c>
       <c r="G48">
-        <v>-7.032278537915886</v>
+        <v>-6.796279678057861</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-3.564201464767214</v>
       </c>
       <c r="E49">
-        <v>-15.878675036521</v>
+        <v>-14.88794455007089</v>
       </c>
       <c r="F49">
-        <v>-0.1589516647912827</v>
+        <v>-0.4235311179953008</v>
       </c>
       <c r="G49">
-        <v>-7.147776850689979</v>
+        <v>-7.435628785329609</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-3.440089284008658</v>
       </c>
       <c r="E50">
-        <v>-16.07257523658143</v>
+        <v>-14.63098082097964</v>
       </c>
       <c r="F50">
-        <v>-0.3991784721335884</v>
+        <v>-0.6377661438534143</v>
       </c>
       <c r="G50">
-        <v>-7.380127489363727</v>
+        <v>-6.276821977490819</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-3.372273160892391</v>
       </c>
       <c r="E51">
-        <v>-13.56584750658352</v>
+        <v>-14.6788920759808</v>
       </c>
       <c r="F51">
-        <v>-0.4089982406622707</v>
+        <v>-0.6011073111757798</v>
       </c>
       <c r="G51">
-        <v>-6.92619541665548</v>
+        <v>-7.233559706703574</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-3.371374641958056</v>
       </c>
       <c r="E52">
-        <v>-14.46745762456267</v>
+        <v>-14.50316917058716</v>
       </c>
       <c r="F52">
-        <v>-0.677004041614342</v>
+        <v>-0.5689659996219362</v>
       </c>
       <c r="G52">
-        <v>-6.853840133349169</v>
+        <v>-6.946191111712678</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-3.440936245700738</v>
       </c>
       <c r="E53">
-        <v>-13.75097605249109</v>
+        <v>-14.38990750718131</v>
       </c>
       <c r="F53">
-        <v>-0.3892050841311085</v>
+        <v>-0.1208286959948243</v>
       </c>
       <c r="G53">
-        <v>-6.918604335733931</v>
+        <v>-6.246921130180121</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-3.581783586943497</v>
       </c>
       <c r="E54">
-        <v>-13.46111295973412</v>
+        <v>-13.32682559151066</v>
       </c>
       <c r="F54">
-        <v>-0.5298730109522711</v>
+        <v>-0.5657977959380995</v>
       </c>
       <c r="G54">
-        <v>-7.433265055814569</v>
+        <v>-7.965925211992224</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-3.795079472467136</v>
       </c>
       <c r="E55">
-        <v>-13.55581240818252</v>
+        <v>-11.97275752152913</v>
       </c>
       <c r="F55">
-        <v>-0.6433067389985793</v>
+        <v>-0.6306901458232309</v>
       </c>
       <c r="G55">
-        <v>-7.004479887022626</v>
+        <v>-6.875335505535657</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-4.075842461156584</v>
       </c>
       <c r="E56">
-        <v>-13.69250892457806</v>
+        <v>-12.13801059501704</v>
       </c>
       <c r="F56">
-        <v>-0.5527654799599483</v>
+        <v>-0.01919278516558232</v>
       </c>
       <c r="G56">
-        <v>-7.711460129116145</v>
+        <v>-6.388076170883566</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-4.417250020094915</v>
       </c>
       <c r="E57">
-        <v>-12.70669636090028</v>
+        <v>-12.6318452140275</v>
       </c>
       <c r="F57">
-        <v>-0.5844570190338071</v>
+        <v>-0.7465334824198802</v>
       </c>
       <c r="G57">
-        <v>-7.403811132151674</v>
+        <v>-7.188748162283999</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-4.813643036009822</v>
       </c>
       <c r="E58">
-        <v>-12.76672128387195</v>
+        <v>-12.42710837566671</v>
       </c>
       <c r="F58">
-        <v>-0.4927596546769054</v>
+        <v>-0.5144002041584277</v>
       </c>
       <c r="G58">
-        <v>-8.218397346453663</v>
+        <v>-7.021158415449474</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-5.252041327789095</v>
       </c>
       <c r="E59">
-        <v>-12.4495922491148</v>
+        <v>-10.29101360082658</v>
       </c>
       <c r="F59">
-        <v>-0.2768957872847624</v>
+        <v>-0.6383030201587483</v>
       </c>
       <c r="G59">
-        <v>-7.148419096524598</v>
+        <v>-7.087687138606667</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-5.715276343314505</v>
       </c>
       <c r="E60">
-        <v>-12.40969186463321</v>
+        <v>-11.13174291424661</v>
       </c>
       <c r="F60">
-        <v>-0.8853540162906827</v>
+        <v>-0.4011588963808455</v>
       </c>
       <c r="G60">
-        <v>-7.12655625378325</v>
+        <v>-6.841587804308326</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-6.188326700742048</v>
       </c>
       <c r="E61">
-        <v>-12.09716375946785</v>
+        <v>-11.06328144419865</v>
       </c>
       <c r="F61">
-        <v>-0.3156585732710583</v>
+        <v>-0.5887005590342271</v>
       </c>
       <c r="G61">
-        <v>-8.1365540396318</v>
+        <v>-7.898320561534768</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-6.654302957504613</v>
       </c>
       <c r="E62">
-        <v>-11.91410019770777</v>
+        <v>-10.95621926170931</v>
       </c>
       <c r="F62">
-        <v>-0.3229436204820798</v>
+        <v>-0.1521670686495401</v>
       </c>
       <c r="G62">
-        <v>-7.782176692380516</v>
+        <v>-7.948157514082956</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-7.097556324269262</v>
       </c>
       <c r="E63">
-        <v>-11.87312203641237</v>
+        <v>-10.7554221957352</v>
       </c>
       <c r="F63">
-        <v>-0.536761339831475</v>
+        <v>-0.9904740801338914</v>
       </c>
       <c r="G63">
-        <v>-8.012617146278105</v>
+        <v>-7.312992936372847</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-7.506082783078227</v>
       </c>
       <c r="E64">
-        <v>-11.21096856701081</v>
+        <v>-10.18715757793467</v>
       </c>
       <c r="F64">
-        <v>-0.4079997140825861</v>
+        <v>-0.6913959691208981</v>
       </c>
       <c r="G64">
-        <v>-7.625035027267931</v>
+        <v>-7.677887886802395</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-7.866238216852908</v>
       </c>
       <c r="E65">
-        <v>-10.62325868182134</v>
+        <v>-10.7937964844762</v>
       </c>
       <c r="F65">
-        <v>-0.624070255096694</v>
+        <v>-0.9082654897693451</v>
       </c>
       <c r="G65">
-        <v>-8.230388142396903</v>
+        <v>-8.731949033778646</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-8.16723955551819</v>
       </c>
       <c r="E66">
-        <v>-11.93327375665625</v>
+        <v>-10.84084280094189</v>
       </c>
       <c r="F66">
-        <v>-0.6198385928906398</v>
+        <v>-0.8199018263644434</v>
       </c>
       <c r="G66">
-        <v>-8.403340973005047</v>
+        <v>-7.672286443749949</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-8.404687609089695</v>
       </c>
       <c r="E67">
-        <v>-11.08211989607056</v>
+        <v>-9.68902543709093</v>
       </c>
       <c r="F67">
-        <v>-0.4586347514639739</v>
+        <v>-0.5007058991076228</v>
       </c>
       <c r="G67">
-        <v>-8.108636209099126</v>
+        <v>-8.528532563118127</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-8.572957798459775</v>
       </c>
       <c r="E68">
-        <v>-11.47549937616887</v>
+        <v>-9.729233757805035</v>
       </c>
       <c r="F68">
-        <v>-0.7018207133092782</v>
+        <v>-0.7059906109846302</v>
       </c>
       <c r="G68">
-        <v>-8.272216885285594</v>
+        <v>-7.620092382777799</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-8.66746892774303</v>
       </c>
       <c r="E69">
-        <v>-10.79294513136276</v>
+        <v>-10.58328131328163</v>
       </c>
       <c r="F69">
-        <v>-0.6424119451563559</v>
+        <v>-0.702454195675454</v>
       </c>
       <c r="G69">
-        <v>-8.267270930249923</v>
+        <v>-8.357102583458047</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-8.687819729798493</v>
       </c>
       <c r="E70">
-        <v>-10.02143807162397</v>
+        <v>-9.997758681037864</v>
       </c>
       <c r="F70">
-        <v>-0.6045970071604505</v>
+        <v>-0.6450218925050002</v>
       </c>
       <c r="G70">
-        <v>-8.590555633796372</v>
+        <v>-7.621694686818807</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-8.634732403630139</v>
       </c>
       <c r="E71">
-        <v>-11.42051917324175</v>
+        <v>-10.26833953147018</v>
       </c>
       <c r="F71">
-        <v>-0.7013519363583082</v>
+        <v>-0.6033324179869721</v>
       </c>
       <c r="G71">
-        <v>-8.273004795123942</v>
+        <v>-8.517273397739066</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-8.513332812879931</v>
       </c>
       <c r="E72">
-        <v>-11.33792886428985</v>
+        <v>-10.57781544515437</v>
       </c>
       <c r="F72">
-        <v>-0.7767007045501284</v>
+        <v>-0.8938403044385649</v>
       </c>
       <c r="G72">
-        <v>-8.496046179741258</v>
+        <v>-8.091494204296781</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-8.332882862401206</v>
       </c>
       <c r="E73">
-        <v>-11.07005151284012</v>
+        <v>-9.863684151092768</v>
       </c>
       <c r="F73">
-        <v>-0.8789281295387871</v>
+        <v>-1.054584079296796</v>
       </c>
       <c r="G73">
-        <v>-8.322957616766004</v>
+        <v>-8.281840641168255</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-8.100832640035398</v>
       </c>
       <c r="E74">
-        <v>-9.684823013211812</v>
+        <v>-11.16811561747622</v>
       </c>
       <c r="F74">
-        <v>-0.8995432294400624</v>
+        <v>-0.7115969299252859</v>
       </c>
       <c r="G74">
-        <v>-8.208604752748499</v>
+        <v>-7.619125703480332</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-7.826918863227232</v>
       </c>
       <c r="E75">
-        <v>-11.16610044654281</v>
+        <v>-11.91333035712647</v>
       </c>
       <c r="F75">
-        <v>-0.9873145868325897</v>
+        <v>-1.47690143353154</v>
       </c>
       <c r="G75">
-        <v>-8.208776901116542</v>
+        <v>-8.78121326194854</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-7.524276747103599</v>
       </c>
       <c r="E76">
-        <v>-12.4580378531391</v>
+        <v>-11.74625683708748</v>
       </c>
       <c r="F76">
-        <v>-1.305828728692814</v>
+        <v>-1.496000135018782</v>
       </c>
       <c r="G76">
-        <v>-8.32184527346481</v>
+        <v>-8.111496520445057</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-7.20329120374814</v>
       </c>
       <c r="E77">
-        <v>-11.56314346211332</v>
+        <v>-12.05830492400803</v>
       </c>
       <c r="F77">
-        <v>-1.349774984140343</v>
+        <v>-1.173913152613327</v>
       </c>
       <c r="G77">
-        <v>-7.952898215295193</v>
+        <v>-7.60637017151752</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-6.873788806053804</v>
       </c>
       <c r="E78">
-        <v>-12.36675740256649</v>
+        <v>-11.15554457363093</v>
       </c>
       <c r="F78">
-        <v>-1.241703684323713</v>
+        <v>-1.159012855507915</v>
       </c>
       <c r="G78">
-        <v>-8.264145775260852</v>
+        <v>-7.673435203052076</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-6.545203974197263</v>
       </c>
       <c r="E79">
-        <v>-13.09567416426313</v>
+        <v>-11.56517674694277</v>
       </c>
       <c r="F79">
-        <v>-1.454412017679343</v>
+        <v>-1.405936363313657</v>
       </c>
       <c r="G79">
-        <v>-8.387463596598703</v>
+        <v>-7.612971399322827</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-6.222849322904163</v>
       </c>
       <c r="E80">
-        <v>-13.33947814788809</v>
+        <v>-12.95792704189782</v>
       </c>
       <c r="F80">
-        <v>-1.333727292099195</v>
+        <v>-1.627993312688125</v>
       </c>
       <c r="G80">
-        <v>-8.516982069731609</v>
+        <v>-7.646593299819665</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-5.911816046845851</v>
       </c>
       <c r="E81">
-        <v>-14.36477447643874</v>
+        <v>-12.82477179217628</v>
       </c>
       <c r="F81">
-        <v>-1.63376671260286</v>
+        <v>-1.699237115147127</v>
       </c>
       <c r="G81">
-        <v>-8.024412620034528</v>
+        <v>-8.087054762728618</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-5.617880816543093</v>
       </c>
       <c r="E82">
-        <v>-14.7310872673932</v>
+        <v>-13.71501544039618</v>
       </c>
       <c r="F82">
-        <v>-1.497065177246915</v>
+        <v>-1.543341855949014</v>
       </c>
       <c r="G82">
-        <v>-8.634115792002103</v>
+        <v>-7.923368149084894</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-5.343781648841268</v>
       </c>
       <c r="E83">
-        <v>-15.4976990467297</v>
+        <v>-14.53268123569514</v>
       </c>
       <c r="F83">
-        <v>-1.539018338799864</v>
+        <v>-1.860859054935469</v>
       </c>
       <c r="G83">
-        <v>-8.2286765903531</v>
+        <v>-7.713923174997363</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-5.09152673985214</v>
       </c>
       <c r="E84">
-        <v>-16.46874878514247</v>
+        <v>-15.98137177006694</v>
       </c>
       <c r="F84">
-        <v>-1.751093981642276</v>
+        <v>-1.817425128351584</v>
       </c>
       <c r="G84">
-        <v>-8.234774615236438</v>
+        <v>-7.345065501557306</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-4.865030707720138</v>
       </c>
       <c r="E85">
-        <v>-17.09204341908421</v>
+        <v>-16.11343112907863</v>
       </c>
       <c r="F85">
-        <v>-1.901500907990433</v>
+        <v>-1.790683462116431</v>
       </c>
       <c r="G85">
-        <v>-8.22267788183594</v>
+        <v>-7.060855167010875</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-4.668282165259299</v>
       </c>
       <c r="E86">
-        <v>-17.71459538328869</v>
+        <v>-18.08515588286235</v>
       </c>
       <c r="F86">
-        <v>-2.112257323805284</v>
+        <v>-1.94916728863333</v>
       </c>
       <c r="G86">
-        <v>-7.629639996113057</v>
+        <v>-7.519680226026165</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-4.505196275092505</v>
       </c>
       <c r="E87">
-        <v>-19.34126400310995</v>
+        <v>-18.64687232724779</v>
       </c>
       <c r="F87">
-        <v>-2.435098150226489</v>
+        <v>-2.109330635273552</v>
       </c>
       <c r="G87">
-        <v>-8.098976037215534</v>
+        <v>-7.514178099339897</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-4.382228335654988</v>
       </c>
       <c r="E88">
-        <v>-20.33916759238821</v>
+        <v>-21.11864023790648</v>
       </c>
       <c r="F88">
-        <v>-2.200636824269341</v>
+        <v>-2.199506058245717</v>
       </c>
       <c r="G88">
-        <v>-7.542446847699733</v>
+        <v>-6.641584506098797</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-4.307820958546762</v>
       </c>
       <c r="E89">
-        <v>-22.02271384574581</v>
+        <v>-20.48969859687718</v>
       </c>
       <c r="F89">
-        <v>-2.221668438826376</v>
+        <v>-2.567351847518922</v>
       </c>
       <c r="G89">
-        <v>-7.588913664888943</v>
+        <v>-6.588890552750217</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-4.287966168966752</v>
       </c>
       <c r="E90">
-        <v>-23.52150288806447</v>
+        <v>-21.86203000253164</v>
       </c>
       <c r="F90">
-        <v>-2.387822153091748</v>
+        <v>-2.384638112348757</v>
       </c>
       <c r="G90">
-        <v>-7.726211920039137</v>
+        <v>-7.122027427485528</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-4.328445112422059</v>
       </c>
       <c r="E91">
-        <v>-25.15287206390569</v>
+        <v>-24.62041409008381</v>
       </c>
       <c r="F91">
-        <v>-2.502882347113212</v>
+        <v>-2.424922047866833</v>
       </c>
       <c r="G91">
-        <v>-7.747932409322296</v>
+        <v>-6.700863134524987</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-4.438316479084143</v>
       </c>
       <c r="E92">
-        <v>-26.68315211447369</v>
+        <v>-25.22387853634596</v>
       </c>
       <c r="F92">
-        <v>-2.669363888503081</v>
+        <v>-2.512809015791187</v>
       </c>
       <c r="G92">
-        <v>-7.64189563569944</v>
+        <v>-7.281066035192116</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-4.621476274325039</v>
       </c>
       <c r="E93">
-        <v>-28.97134474580944</v>
+        <v>-28.90973938540909</v>
       </c>
       <c r="F93">
-        <v>-2.796610699543852</v>
+        <v>-2.552080963229297</v>
       </c>
       <c r="G93">
-        <v>-8.67787458294019</v>
+        <v>-7.206833672565038</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-4.880041893342709</v>
       </c>
       <c r="E94">
-        <v>-30.83154903444327</v>
+        <v>-29.96844453095134</v>
       </c>
       <c r="F94">
-        <v>-2.76335049976075</v>
+        <v>-2.551484697952134</v>
       </c>
       <c r="G94">
-        <v>-8.135696608337129</v>
+        <v>-7.045676315713316</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-5.21740750556176</v>
       </c>
       <c r="E95">
-        <v>-33.00462106379303</v>
+        <v>-32.49184610224549</v>
       </c>
       <c r="F95">
-        <v>-2.720574602984731</v>
+        <v>-3.063015373815414</v>
       </c>
       <c r="G95">
-        <v>-8.626931908181884</v>
+        <v>-8.651956321913236</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-5.637059353087039</v>
       </c>
       <c r="E96">
-        <v>-35.60762188695701</v>
+        <v>-34.80225316282587</v>
       </c>
       <c r="F96">
-        <v>-2.69398497251746</v>
+        <v>-3.302132003310996</v>
       </c>
       <c r="G96">
-        <v>-8.321481113455489</v>
+        <v>-7.110917236655734</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-6.124466783265011</v>
       </c>
       <c r="E97">
-        <v>-37.17610640849072</v>
+        <v>-36.54555036647768</v>
       </c>
       <c r="F97">
-        <v>-2.614386329501558</v>
+        <v>-2.880529692297072</v>
       </c>
       <c r="G97">
-        <v>-8.319190215942314</v>
+        <v>-8.219738117397068</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-6.696357351082024</v>
       </c>
       <c r="E98">
-        <v>-41.05333377640699</v>
+        <v>-40.06494451101885</v>
       </c>
       <c r="F98">
-        <v>-2.702857684908709</v>
+        <v>-3.103093427564482</v>
       </c>
       <c r="G98">
-        <v>-8.392833301463401</v>
+        <v>-7.758122268492172</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-7.317104160296641</v>
       </c>
       <c r="E99">
-        <v>-42.56324927936249</v>
+        <v>-41.65423737061781</v>
       </c>
       <c r="F99">
-        <v>-3.100560289952737</v>
+        <v>-2.805416896286653</v>
       </c>
       <c r="G99">
-        <v>-9.160823587300149</v>
+        <v>-9.380799406748102</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-8.01638567565297</v>
       </c>
       <c r="E100">
-        <v>-46.04185319427958</v>
+        <v>-45.30250735694327</v>
       </c>
       <c r="F100">
-        <v>-2.574906916588525</v>
+        <v>-2.926095287043138</v>
       </c>
       <c r="G100">
-        <v>-9.071276641008403</v>
+        <v>-9.175303913488921</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-8.715788780645562</v>
       </c>
       <c r="E101">
-        <v>-47.19031722312785</v>
+        <v>-47.33086747090392</v>
       </c>
       <c r="F101">
-        <v>-2.911183112143361</v>
+        <v>-2.986278487388711</v>
       </c>
       <c r="G101">
-        <v>-10.74946500686683</v>
+        <v>-9.624419142437528</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-9.508330695123623</v>
       </c>
       <c r="E102">
-        <v>-50.19459971353352</v>
+        <v>-50.51565040678132</v>
       </c>
       <c r="F102">
-        <v>-2.657779871584599</v>
+        <v>-2.80523714566525</v>
       </c>
       <c r="G102">
-        <v>-10.34555858780251</v>
+        <v>-9.073471532700939</v>
       </c>
     </row>
   </sheetData>
